--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -2540,10 +2540,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119587429</v>
+        <v>119586168</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>8432</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2556,37 +2556,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480241</v>
+        <v>480216</v>
       </c>
       <c r="R20" t="n">
-        <v>6827511</v>
+        <v>6827581</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2613,9 +2618,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2630,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119586168</v>
+        <v>119587429</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2658,42 +2673,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480216</v>
+        <v>480241</v>
       </c>
       <c r="R21" t="n">
-        <v>6827581</v>
+        <v>6827511</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2720,19 +2730,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2747,12 +2747,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119586446</v>
+        <v>119587161</v>
       </c>
       <c r="B38" t="n">
-        <v>82305</v>
+        <v>5169</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4437,41 +4437,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1312</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480268</v>
+        <v>480388</v>
       </c>
       <c r="R38" t="n">
-        <v>6827557</v>
+        <v>6827441</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4527,10 +4532,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119586658</v>
+        <v>119586446</v>
       </c>
       <c r="B39" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4543,34 +4548,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480377</v>
+        <v>480268</v>
       </c>
       <c r="R39" t="n">
-        <v>6827539</v>
+        <v>6827557</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4629,10 +4634,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119586591</v>
+        <v>119586658</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4641,25 +4646,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4669,10 +4674,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480309</v>
+        <v>480377</v>
       </c>
       <c r="R40" t="n">
-        <v>6827520</v>
+        <v>6827539</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4731,10 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119587161</v>
+        <v>119586591</v>
       </c>
       <c r="B41" t="n">
-        <v>5169</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4747,42 +4752,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480388</v>
+        <v>480309</v>
       </c>
       <c r="R41" t="n">
-        <v>6827441</v>
+        <v>6827520</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -1622,10 +1622,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119585186</v>
+        <v>119587602</v>
       </c>
       <c r="B11" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1638,21 +1638,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480155</v>
+        <v>480173</v>
       </c>
       <c r="R11" t="n">
-        <v>6827454</v>
+        <v>6827470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119587431</v>
+        <v>119585186</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480241</v>
+        <v>480155</v>
       </c>
       <c r="R12" t="n">
-        <v>6827511</v>
+        <v>6827454</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119587602</v>
+        <v>119587431</v>
       </c>
       <c r="B13" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1842,21 +1842,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480173</v>
+        <v>480241</v>
       </c>
       <c r="R13" t="n">
-        <v>6827470</v>
+        <v>6827511</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119585956</v>
+        <v>119585182</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3806,50 +3806,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480186</v>
+        <v>480155</v>
       </c>
       <c r="R32" t="n">
-        <v>6827553</v>
+        <v>6827454</v>
       </c>
       <c r="S32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3876,19 +3867,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3903,22 +3884,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119585182</v>
+        <v>119585956</v>
       </c>
       <c r="B33" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3927,41 +3908,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480155</v>
+        <v>480186</v>
       </c>
       <c r="R33" t="n">
-        <v>6827454</v>
+        <v>6827553</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3988,9 +3978,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,12 +4005,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119585463</v>
+        <v>119587254</v>
       </c>
       <c r="B2" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480192</v>
+        <v>480368</v>
       </c>
       <c r="R2" t="n">
-        <v>6827498</v>
+        <v>6827434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119586225</v>
+        <v>119587585</v>
       </c>
       <c r="B3" t="n">
-        <v>78560</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480247</v>
+        <v>480184</v>
       </c>
       <c r="R3" t="n">
-        <v>6827581</v>
+        <v>6827450</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +859,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +886,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119587163</v>
+        <v>119587413</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -915,17 +934,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480388</v>
+        <v>480309</v>
       </c>
       <c r="R4" t="n">
-        <v>6827441</v>
+        <v>6827520</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119587585</v>
+        <v>119587431</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,46 +1016,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480184</v>
+        <v>480241</v>
       </c>
       <c r="R5" t="n">
-        <v>6827450</v>
+        <v>6827511</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,19 +1073,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,19 +1090,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119586177</v>
+        <v>119587179</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480220</v>
+        <v>480380</v>
       </c>
       <c r="R6" t="n">
-        <v>6827593</v>
+        <v>6827425</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119587094</v>
+        <v>119586076</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,34 +1220,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480375</v>
+        <v>480203</v>
       </c>
       <c r="R7" t="n">
-        <v>6827471</v>
+        <v>6827559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119587607</v>
+        <v>119586225</v>
       </c>
       <c r="B8" t="n">
-        <v>77910</v>
+        <v>78560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480173</v>
+        <v>480247</v>
       </c>
       <c r="R8" t="n">
-        <v>6827470</v>
+        <v>6827581</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119587775</v>
+        <v>119586187</v>
       </c>
       <c r="B9" t="n">
-        <v>78262</v>
+        <v>78560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,37 +1424,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480151</v>
+        <v>480220</v>
       </c>
       <c r="R9" t="n">
-        <v>6827452</v>
+        <v>6827593</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1481,19 +1481,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1508,22 +1498,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119586966</v>
+        <v>119586168</v>
       </c>
       <c r="B10" t="n">
-        <v>91884</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,41 +1522,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480330</v>
+        <v>480216</v>
       </c>
       <c r="R10" t="n">
-        <v>6827548</v>
+        <v>6827581</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1593,9 +1588,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1610,22 +1615,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119587602</v>
+        <v>119586591</v>
       </c>
       <c r="B11" t="n">
-        <v>77458</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,38 +1639,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480173</v>
+        <v>480309</v>
       </c>
       <c r="R11" t="n">
-        <v>6827470</v>
+        <v>6827520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1724,10 +1729,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119585186</v>
+        <v>119586966</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1740,34 +1745,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480155</v>
+        <v>480330</v>
       </c>
       <c r="R12" t="n">
-        <v>6827454</v>
+        <v>6827548</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1831,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119587431</v>
+        <v>119586241</v>
       </c>
       <c r="B13" t="n">
         <v>78526</v>
@@ -1866,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480241</v>
+        <v>480249</v>
       </c>
       <c r="R13" t="n">
-        <v>6827511</v>
+        <v>6827569</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1928,10 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119587206</v>
+        <v>119586446</v>
       </c>
       <c r="B14" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1944,21 +1949,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480417</v>
+        <v>480268</v>
       </c>
       <c r="R14" t="n">
-        <v>6827436</v>
+        <v>6827557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2030,10 +2035,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119587683</v>
+        <v>119587163</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,25 +2047,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2070,13 +2075,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480155</v>
+        <v>480388</v>
       </c>
       <c r="R15" t="n">
-        <v>6827454</v>
+        <v>6827441</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2132,10 +2137,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119586559</v>
+        <v>119587775</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2148,37 +2153,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480309</v>
+        <v>480151</v>
       </c>
       <c r="R16" t="n">
-        <v>6827520</v>
+        <v>6827452</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2205,9 +2210,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2222,22 +2237,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119586273</v>
+        <v>119585762</v>
       </c>
       <c r="B17" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2250,21 +2265,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2274,10 +2289,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480268</v>
+        <v>480196</v>
       </c>
       <c r="R17" t="n">
-        <v>6827557</v>
+        <v>6827538</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,10 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119586928</v>
+        <v>119585463</v>
       </c>
       <c r="B18" t="n">
-        <v>77458</v>
+        <v>78560</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2352,34 +2367,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480330</v>
+        <v>480192</v>
       </c>
       <c r="R18" t="n">
-        <v>6827548</v>
+        <v>6827498</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2453,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119586193</v>
+        <v>119586520</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,38 +2465,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480220</v>
+        <v>480299</v>
       </c>
       <c r="R19" t="n">
-        <v>6827593</v>
+        <v>6827540</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,10 +2555,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119586168</v>
+        <v>119586928</v>
       </c>
       <c r="B20" t="n">
-        <v>8432</v>
+        <v>77458</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,46 +2567,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480216</v>
+        <v>480330</v>
       </c>
       <c r="R20" t="n">
-        <v>6827581</v>
+        <v>6827548</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2618,19 +2628,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,22 +2645,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119587429</v>
+        <v>119586658</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,38 +2669,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480241</v>
+        <v>480377</v>
       </c>
       <c r="R21" t="n">
-        <v>6827511</v>
+        <v>6827539</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119585602</v>
+        <v>119585186</v>
       </c>
       <c r="B22" t="n">
         <v>78526</v>
@@ -2795,17 +2795,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480202</v>
+        <v>480155</v>
       </c>
       <c r="R22" t="n">
-        <v>6827537</v>
+        <v>6827454</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2832,19 +2832,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2859,22 +2849,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119585762</v>
+        <v>119587342</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,38 +2873,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480196</v>
+        <v>480362</v>
       </c>
       <c r="R23" t="n">
-        <v>6827538</v>
+        <v>6827489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,7 +2963,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119587342</v>
+        <v>119587683</v>
       </c>
       <c r="B24" t="n">
         <v>91840</v>
@@ -3009,14 +2999,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480362</v>
+        <v>480155</v>
       </c>
       <c r="R24" t="n">
-        <v>6827489</v>
+        <v>6827454</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119586076</v>
+        <v>119587602</v>
       </c>
       <c r="B25" t="n">
-        <v>78262</v>
+        <v>77458</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3091,21 +3081,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3115,10 +3105,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480203</v>
+        <v>480173</v>
       </c>
       <c r="R25" t="n">
-        <v>6827559</v>
+        <v>6827470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3177,10 +3167,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119585255</v>
+        <v>119586694</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3193,34 +3183,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480178</v>
+        <v>480364</v>
       </c>
       <c r="R26" t="n">
-        <v>6827488</v>
+        <v>6827541</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3279,7 +3269,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119586108</v>
+        <v>119586177</v>
       </c>
       <c r="B27" t="n">
         <v>78526</v>
@@ -3319,10 +3309,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480218</v>
+        <v>480220</v>
       </c>
       <c r="R27" t="n">
-        <v>6827576</v>
+        <v>6827593</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3381,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119587157</v>
+        <v>119587094</v>
       </c>
       <c r="B28" t="n">
-        <v>5189</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,46 +3383,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480388</v>
+        <v>480375</v>
       </c>
       <c r="R28" t="n">
-        <v>6827441</v>
+        <v>6827471</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3488,10 +3473,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119586694</v>
+        <v>119586193</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3500,38 +3485,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480364</v>
+        <v>480220</v>
       </c>
       <c r="R29" t="n">
-        <v>6827541</v>
+        <v>6827593</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,7 +3575,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119587254</v>
+        <v>119585640</v>
       </c>
       <c r="B30" t="n">
         <v>91840</v>
@@ -3630,10 +3615,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480368</v>
+        <v>480227</v>
       </c>
       <c r="R30" t="n">
-        <v>6827434</v>
+        <v>6827526</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3692,10 +3677,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119585640</v>
+        <v>119587206</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3704,25 +3689,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3732,10 +3717,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480227</v>
+        <v>480417</v>
       </c>
       <c r="R31" t="n">
-        <v>6827526</v>
+        <v>6827436</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3896,7 +3881,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119585956</v>
+        <v>119587429</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -3929,29 +3914,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480186</v>
+        <v>480241</v>
       </c>
       <c r="R33" t="n">
-        <v>6827553</v>
+        <v>6827511</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3978,19 +3954,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4005,22 +3971,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119587179</v>
+        <v>119587456</v>
       </c>
       <c r="B34" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4033,21 +3999,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4057,10 +4023,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480380</v>
+        <v>480211</v>
       </c>
       <c r="R34" t="n">
-        <v>6827425</v>
+        <v>6827485</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4119,10 +4085,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119586241</v>
+        <v>119587157</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>5189</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4131,41 +4097,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480249</v>
+        <v>480388</v>
       </c>
       <c r="R35" t="n">
-        <v>6827569</v>
+        <v>6827441</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4221,10 +4192,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119587438</v>
+        <v>119587161</v>
       </c>
       <c r="B36" t="n">
-        <v>96868</v>
+        <v>5169</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4237,37 +4208,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480241</v>
+        <v>480388</v>
       </c>
       <c r="R36" t="n">
-        <v>6827511</v>
+        <v>6827441</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4323,7 +4299,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119586520</v>
+        <v>119585602</v>
       </c>
       <c r="B37" t="n">
         <v>78526</v>
@@ -4359,17 +4335,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480299</v>
+        <v>480202</v>
       </c>
       <c r="R37" t="n">
-        <v>6827540</v>
+        <v>6827537</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4396,9 +4372,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4413,22 +4399,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119587161</v>
+        <v>119586273</v>
       </c>
       <c r="B38" t="n">
-        <v>5169</v>
+        <v>74638</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4437,46 +4423,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100526</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480388</v>
+        <v>480268</v>
       </c>
       <c r="R38" t="n">
-        <v>6827441</v>
+        <v>6827557</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4532,10 +4513,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119586446</v>
+        <v>119587024</v>
       </c>
       <c r="B39" t="n">
-        <v>82305</v>
+        <v>91884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,34 +4529,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>5449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480268</v>
+        <v>480345</v>
       </c>
       <c r="R39" t="n">
-        <v>6827557</v>
+        <v>6827502</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4634,7 +4615,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119586658</v>
+        <v>119586108</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4670,14 +4651,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480377</v>
+        <v>480218</v>
       </c>
       <c r="R40" t="n">
-        <v>6827539</v>
+        <v>6827576</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4736,10 +4717,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119586591</v>
+        <v>119585255</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4748,38 +4729,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480309</v>
+        <v>480178</v>
       </c>
       <c r="R41" t="n">
-        <v>6827520</v>
+        <v>6827488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4838,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119586187</v>
+        <v>119585956</v>
       </c>
       <c r="B42" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4850,41 +4831,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480220</v>
+        <v>480186</v>
       </c>
       <c r="R42" t="n">
-        <v>6827593</v>
+        <v>6827553</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4911,9 +4901,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4928,22 +4928,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119587456</v>
+        <v>119587607</v>
       </c>
       <c r="B43" t="n">
-        <v>91884</v>
+        <v>77910</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480211</v>
+        <v>480173</v>
       </c>
       <c r="R43" t="n">
-        <v>6827485</v>
+        <v>6827470</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119587024</v>
+        <v>119587438</v>
       </c>
       <c r="B44" t="n">
-        <v>91884</v>
+        <v>96868</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5054,38 +5054,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480345</v>
+        <v>480241</v>
       </c>
       <c r="R44" t="n">
-        <v>6827502</v>
+        <v>6827511</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5252,10 +5252,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611517</v>
+        <v>119611519</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5268,21 +5268,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5292,10 +5292,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480379</v>
+        <v>480375</v>
       </c>
       <c r="R46" t="n">
-        <v>6827494</v>
+        <v>6827495</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5330,18 +5330,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>10 fk</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5360,10 +5354,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611521</v>
+        <v>119611520</v>
       </c>
       <c r="B47" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5372,25 +5366,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5400,10 +5394,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480342</v>
+        <v>480256</v>
       </c>
       <c r="R47" t="n">
-        <v>6827505</v>
+        <v>6827528</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5438,18 +5432,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>6 fk</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5468,10 +5456,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119611872</v>
+        <v>119611516</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5484,34 +5472,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480180</v>
+        <v>480383</v>
       </c>
       <c r="R48" t="n">
-        <v>6827559</v>
+        <v>6827478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5546,34 +5534,40 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>En fk</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119611516</v>
+        <v>119611521</v>
       </c>
       <c r="B49" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5582,25 +5576,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5610,10 +5604,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480383</v>
+        <v>480342</v>
       </c>
       <c r="R49" t="n">
-        <v>6827478</v>
+        <v>6827505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5650,7 +5644,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>En fk</t>
+          <t>6 fk</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5678,10 +5672,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119586315</v>
+        <v>119611517</v>
       </c>
       <c r="B50" t="n">
-        <v>5189</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5690,41 +5684,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480225</v>
+        <v>480379</v>
       </c>
       <c r="R50" t="n">
-        <v>6827599</v>
+        <v>6827494</v>
       </c>
       <c r="S50" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5751,19 +5745,14 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:34</t>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>10 fk</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5772,28 +5761,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119611520</v>
+        <v>119586315</v>
       </c>
       <c r="B51" t="n">
-        <v>78526</v>
+        <v>5189</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5802,41 +5792,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480256</v>
+        <v>480225</v>
       </c>
       <c r="R51" t="n">
-        <v>6827528</v>
+        <v>6827599</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5863,9 +5853,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5880,22 +5880,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119611866</v>
+        <v>119611870</v>
       </c>
       <c r="B52" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5908,21 +5908,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5932,10 +5932,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480364</v>
+        <v>480264</v>
       </c>
       <c r="R52" t="n">
-        <v>6827460</v>
+        <v>6827609</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6203,10 +6203,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119611870</v>
+        <v>119611866</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6219,21 +6219,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6243,10 +6243,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480264</v>
+        <v>480364</v>
       </c>
       <c r="R55" t="n">
-        <v>6827609</v>
+        <v>6827460</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119611519</v>
+        <v>119611872</v>
       </c>
       <c r="B56" t="n">
         <v>78526</v>
@@ -6341,14 +6341,14 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480375</v>
+        <v>480180</v>
       </c>
       <c r="R56" t="n">
-        <v>6827495</v>
+        <v>6827559</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6395,22 +6395,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119672747</v>
+        <v>119672739</v>
       </c>
       <c r="B57" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6419,25 +6419,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480329</v>
+        <v>480259</v>
       </c>
       <c r="R57" t="n">
-        <v>6827536</v>
+        <v>6827567</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6509,7 +6509,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119672741</v>
+        <v>119672740</v>
       </c>
       <c r="B58" t="n">
         <v>78526</v>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480176</v>
+        <v>480203</v>
       </c>
       <c r="R58" t="n">
-        <v>6827531</v>
+        <v>6827555</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119672724</v>
+        <v>119672738</v>
       </c>
       <c r="B59" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6627,21 +6627,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480212</v>
+        <v>480261</v>
       </c>
       <c r="R59" t="n">
-        <v>6827501</v>
+        <v>6827555</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119672746</v>
+        <v>119672749</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6725,25 +6725,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480170</v>
+        <v>480345</v>
       </c>
       <c r="R60" t="n">
-        <v>6827542</v>
+        <v>6827530</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119672744</v>
+        <v>119672723</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6827,25 +6827,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480179</v>
+        <v>480212</v>
       </c>
       <c r="R61" t="n">
-        <v>6827552</v>
+        <v>6827496</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119672749</v>
+        <v>119672744</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6929,25 +6929,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480345</v>
+        <v>480179</v>
       </c>
       <c r="R62" t="n">
-        <v>6827530</v>
+        <v>6827552</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119672743</v>
+        <v>119672747</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>5169</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480317</v>
+        <v>480329</v>
       </c>
       <c r="R63" t="n">
-        <v>6827518</v>
+        <v>6827536</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119672723</v>
+        <v>119672743</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7133,25 +7133,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480212</v>
+        <v>480317</v>
       </c>
       <c r="R64" t="n">
-        <v>6827496</v>
+        <v>6827518</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119672738</v>
+        <v>119672742</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7235,25 +7235,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480261</v>
+        <v>480349</v>
       </c>
       <c r="R65" t="n">
-        <v>6827555</v>
+        <v>6827514</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119672740</v>
+        <v>119672746</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7337,25 +7337,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480203</v>
+        <v>480170</v>
       </c>
       <c r="R66" t="n">
-        <v>6827555</v>
+        <v>6827542</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7427,10 +7427,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119672739</v>
+        <v>119672724</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7443,21 +7443,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480259</v>
+        <v>480212</v>
       </c>
       <c r="R67" t="n">
-        <v>6827567</v>
+        <v>6827501</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119672742</v>
+        <v>119672737</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7541,25 +7541,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480349</v>
+        <v>480227</v>
       </c>
       <c r="R68" t="n">
-        <v>6827514</v>
+        <v>6827511</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119672737</v>
+        <v>119672741</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480227</v>
+        <v>480176</v>
       </c>
       <c r="R69" t="n">
-        <v>6827511</v>
+        <v>6827531</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119711096</v>
+        <v>119711095</v>
       </c>
       <c r="B70" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480307</v>
+        <v>480290</v>
       </c>
       <c r="R70" t="n">
-        <v>6827579</v>
+        <v>6827524</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7835,10 +7835,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119711093</v>
+        <v>119711100</v>
       </c>
       <c r="B71" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7851,21 +7851,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480165</v>
+        <v>480230</v>
       </c>
       <c r="R71" t="n">
-        <v>6827514</v>
+        <v>6827520</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7937,10 +7937,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119711095</v>
+        <v>119711098</v>
       </c>
       <c r="B72" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7953,21 +7953,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480290</v>
+        <v>480252</v>
       </c>
       <c r="R72" t="n">
-        <v>6827524</v>
+        <v>6827548</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8039,7 +8039,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119711100</v>
+        <v>119711097</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480230</v>
+        <v>480360</v>
       </c>
       <c r="R73" t="n">
-        <v>6827520</v>
+        <v>6827488</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119711098</v>
+        <v>119711093</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8157,21 +8157,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480252</v>
+        <v>480165</v>
       </c>
       <c r="R74" t="n">
-        <v>6827548</v>
+        <v>6827514</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119711097</v>
+        <v>119711096</v>
       </c>
       <c r="B75" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480360</v>
+        <v>480307</v>
       </c>
       <c r="R75" t="n">
-        <v>6827488</v>
+        <v>6827579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -1510,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119586168</v>
+        <v>119586591</v>
       </c>
       <c r="B10" t="n">
-        <v>8432</v>
+        <v>91840</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,42 +1526,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480216</v>
+        <v>480309</v>
       </c>
       <c r="R10" t="n">
-        <v>6827581</v>
+        <v>6827520</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1588,19 +1583,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,22 +1600,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119586591</v>
+        <v>119586966</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480309</v>
+        <v>480330</v>
       </c>
       <c r="R11" t="n">
-        <v>6827520</v>
+        <v>6827548</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1729,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119586966</v>
+        <v>119586241</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1745,34 +1730,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480330</v>
+        <v>480249</v>
       </c>
       <c r="R12" t="n">
-        <v>6827548</v>
+        <v>6827569</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1831,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119586241</v>
+        <v>119586168</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>8432</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,41 +1828,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480249</v>
+        <v>480216</v>
       </c>
       <c r="R13" t="n">
-        <v>6827569</v>
+        <v>6827581</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1904,9 +1894,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,12 +1921,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -3065,10 +3065,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119587602</v>
+        <v>119586177</v>
       </c>
       <c r="B25" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3081,21 +3081,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3105,10 +3105,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480173</v>
+        <v>480220</v>
       </c>
       <c r="R25" t="n">
-        <v>6827470</v>
+        <v>6827593</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,10 +3167,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119586694</v>
+        <v>119587094</v>
       </c>
       <c r="B26" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3183,21 +3183,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480364</v>
+        <v>480375</v>
       </c>
       <c r="R26" t="n">
-        <v>6827541</v>
+        <v>6827471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3269,10 +3269,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119586177</v>
+        <v>119587602</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3285,21 +3285,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3309,10 +3309,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480220</v>
+        <v>480173</v>
       </c>
       <c r="R27" t="n">
-        <v>6827593</v>
+        <v>6827470</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119587094</v>
+        <v>119586694</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3387,21 +3387,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3411,10 +3411,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480375</v>
+        <v>480364</v>
       </c>
       <c r="R28" t="n">
-        <v>6827471</v>
+        <v>6827541</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119587429</v>
+        <v>119587157</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>5189</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3897,37 +3897,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>105930</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480241</v>
+        <v>480388</v>
       </c>
       <c r="R33" t="n">
-        <v>6827511</v>
+        <v>6827441</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3983,10 +3988,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119587456</v>
+        <v>119587429</v>
       </c>
       <c r="B34" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3995,25 +4000,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4023,10 +4028,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480211</v>
+        <v>480241</v>
       </c>
       <c r="R34" t="n">
-        <v>6827485</v>
+        <v>6827511</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4085,10 +4090,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119587157</v>
+        <v>119587456</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>91884</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4097,46 +4102,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480388</v>
+        <v>480211</v>
       </c>
       <c r="R35" t="n">
-        <v>6827441</v>
+        <v>6827485</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119585602</v>
+        <v>119586273</v>
       </c>
       <c r="B37" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,37 +4315,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480202</v>
+        <v>480268</v>
       </c>
       <c r="R37" t="n">
-        <v>6827537</v>
+        <v>6827557</v>
       </c>
       <c r="S37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4372,19 +4372,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4399,22 +4389,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119586273</v>
+        <v>119585602</v>
       </c>
       <c r="B38" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4427,37 +4417,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480268</v>
+        <v>480202</v>
       </c>
       <c r="R38" t="n">
-        <v>6827557</v>
+        <v>6827537</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4484,9 +4474,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4501,12 +4501,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4819,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119585956</v>
+        <v>119587438</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4835,46 +4835,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480186</v>
+        <v>480241</v>
       </c>
       <c r="R42" t="n">
-        <v>6827553</v>
+        <v>6827511</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4901,19 +4892,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4928,22 +4909,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119587607</v>
+        <v>119585956</v>
       </c>
       <c r="B43" t="n">
-        <v>77910</v>
+        <v>91840</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4952,41 +4933,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480173</v>
+        <v>480186</v>
       </c>
       <c r="R43" t="n">
-        <v>6827470</v>
+        <v>6827553</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5013,9 +5003,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5030,22 +5030,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119587438</v>
+        <v>119587607</v>
       </c>
       <c r="B44" t="n">
-        <v>96868</v>
+        <v>77910</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5054,25 +5054,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480241</v>
+        <v>480173</v>
       </c>
       <c r="R44" t="n">
-        <v>6827511</v>
+        <v>6827470</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119711100</v>
+        <v>119711098</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>480230</v>
+        <v>480252</v>
       </c>
       <c r="R71" t="n">
-        <v>6827520</v>
+        <v>6827548</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119711098</v>
+        <v>119711100</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480252</v>
+        <v>480230</v>
       </c>
       <c r="R72" t="n">
-        <v>6827548</v>
+        <v>6827520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119587254</v>
+        <v>119586928</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>77458</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480368</v>
+        <v>480330</v>
       </c>
       <c r="R2" t="n">
-        <v>6827434</v>
+        <v>6827548</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119587585</v>
+        <v>119585956</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,30 +789,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -822,14 +822,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480184</v>
+        <v>480186</v>
       </c>
       <c r="R3" t="n">
-        <v>6827450</v>
+        <v>6827553</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119587413</v>
+        <v>119587206</v>
       </c>
       <c r="B4" t="n">
         <v>78526</v>
@@ -934,14 +934,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480309</v>
+        <v>480417</v>
       </c>
       <c r="R4" t="n">
-        <v>6827520</v>
+        <v>6827436</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119587431</v>
+        <v>119587585</v>
       </c>
       <c r="B5" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,37 +1016,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480241</v>
+        <v>480184</v>
       </c>
       <c r="R5" t="n">
-        <v>6827511</v>
+        <v>6827450</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,9 +1082,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1090,22 +1109,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119587179</v>
+        <v>119586591</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,38 +1133,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480380</v>
+        <v>480309</v>
       </c>
       <c r="R6" t="n">
-        <v>6827425</v>
+        <v>6827520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119586076</v>
+        <v>119585640</v>
       </c>
       <c r="B7" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,25 +1235,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480203</v>
+        <v>480227</v>
       </c>
       <c r="R7" t="n">
-        <v>6827559</v>
+        <v>6827526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119586225</v>
+        <v>119586966</v>
       </c>
       <c r="B8" t="n">
-        <v>78560</v>
+        <v>91884</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,34 +1341,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>5449</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480247</v>
+        <v>480330</v>
       </c>
       <c r="R8" t="n">
-        <v>6827581</v>
+        <v>6827548</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119586187</v>
+        <v>119586559</v>
       </c>
       <c r="B9" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,34 +1443,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480220</v>
+        <v>480309</v>
       </c>
       <c r="R9" t="n">
-        <v>6827593</v>
+        <v>6827520</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1529,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119586591</v>
+        <v>119587179</v>
       </c>
       <c r="B10" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,38 +1541,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480309</v>
+        <v>480380</v>
       </c>
       <c r="R10" t="n">
-        <v>6827520</v>
+        <v>6827425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1612,10 +1631,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119586966</v>
+        <v>119586193</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,38 +1643,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480330</v>
+        <v>480220</v>
       </c>
       <c r="R11" t="n">
-        <v>6827548</v>
+        <v>6827593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1714,7 +1733,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119586241</v>
+        <v>119587163</v>
       </c>
       <c r="B12" t="n">
         <v>78526</v>
@@ -1754,13 +1773,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>480249</v>
+        <v>480388</v>
       </c>
       <c r="R12" t="n">
-        <v>6827569</v>
+        <v>6827441</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1816,10 +1835,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119586168</v>
+        <v>119585186</v>
       </c>
       <c r="B13" t="n">
-        <v>8432</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,46 +1847,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480216</v>
+        <v>480155</v>
       </c>
       <c r="R13" t="n">
-        <v>6827581</v>
+        <v>6827454</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1894,19 +1908,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1921,22 +1925,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119586446</v>
+        <v>119586076</v>
       </c>
       <c r="B14" t="n">
-        <v>82305</v>
+        <v>78262</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1949,21 +1953,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1973,10 +1977,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480268</v>
+        <v>480203</v>
       </c>
       <c r="R14" t="n">
-        <v>6827557</v>
+        <v>6827559</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2035,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119587163</v>
+        <v>119587161</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>5169</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2047,28 +2051,33 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
@@ -2137,10 +2146,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119587775</v>
+        <v>119585762</v>
       </c>
       <c r="B16" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2153,37 +2162,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480151</v>
+        <v>480196</v>
       </c>
       <c r="R16" t="n">
-        <v>6827452</v>
+        <v>6827538</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2210,19 +2219,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2237,22 +2236,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119585762</v>
+        <v>119587775</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2265,37 +2264,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480196</v>
+        <v>480151</v>
       </c>
       <c r="R17" t="n">
-        <v>6827538</v>
+        <v>6827452</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2322,9 +2321,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2339,22 +2348,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119585463</v>
+        <v>119586658</v>
       </c>
       <c r="B18" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2367,34 +2376,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480192</v>
+        <v>480377</v>
       </c>
       <c r="R18" t="n">
-        <v>6827498</v>
+        <v>6827539</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,10 +2462,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119586520</v>
+        <v>119587438</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>96868</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,38 +2474,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480299</v>
+        <v>480241</v>
       </c>
       <c r="R19" t="n">
-        <v>6827540</v>
+        <v>6827511</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2555,10 +2564,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119586928</v>
+        <v>119587157</v>
       </c>
       <c r="B20" t="n">
-        <v>77458</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,41 +2576,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480330</v>
+        <v>480388</v>
       </c>
       <c r="R20" t="n">
-        <v>6827548</v>
+        <v>6827441</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2657,10 +2671,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119586658</v>
+        <v>119587429</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,38 +2683,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480377</v>
+        <v>480241</v>
       </c>
       <c r="R21" t="n">
-        <v>6827539</v>
+        <v>6827511</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119585186</v>
+        <v>119586446</v>
       </c>
       <c r="B22" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2775,21 +2789,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2799,10 +2813,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480155</v>
+        <v>480268</v>
       </c>
       <c r="R22" t="n">
-        <v>6827454</v>
+        <v>6827557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2861,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119587342</v>
+        <v>119586177</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,38 +2887,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480362</v>
+        <v>480220</v>
       </c>
       <c r="R23" t="n">
-        <v>6827489</v>
+        <v>6827593</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2963,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119587683</v>
+        <v>119586108</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,25 +2989,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3003,10 +3017,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480155</v>
+        <v>480218</v>
       </c>
       <c r="R24" t="n">
-        <v>6827454</v>
+        <v>6827576</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3065,7 +3079,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119586177</v>
+        <v>119587094</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3101,14 +3115,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480220</v>
+        <v>480375</v>
       </c>
       <c r="R25" t="n">
-        <v>6827593</v>
+        <v>6827471</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3167,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119587094</v>
+        <v>119585602</v>
       </c>
       <c r="B26" t="n">
         <v>78526</v>
@@ -3203,17 +3217,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480375</v>
+        <v>480202</v>
       </c>
       <c r="R26" t="n">
-        <v>6827471</v>
+        <v>6827537</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3240,9 +3254,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3257,22 +3281,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119587602</v>
+        <v>119585255</v>
       </c>
       <c r="B27" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3285,21 +3309,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3309,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480173</v>
+        <v>480178</v>
       </c>
       <c r="R27" t="n">
-        <v>6827470</v>
+        <v>6827488</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3371,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119586694</v>
+        <v>119586520</v>
       </c>
       <c r="B28" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3387,21 +3411,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3411,10 +3435,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480364</v>
+        <v>480299</v>
       </c>
       <c r="R28" t="n">
-        <v>6827541</v>
+        <v>6827540</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3473,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119586193</v>
+        <v>119587456</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3485,25 +3509,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3513,10 +3537,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480220</v>
+        <v>480211</v>
       </c>
       <c r="R29" t="n">
-        <v>6827593</v>
+        <v>6827485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3575,10 +3599,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119585640</v>
+        <v>119586694</v>
       </c>
       <c r="B30" t="n">
-        <v>91840</v>
+        <v>74638</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3587,38 +3611,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480227</v>
+        <v>480364</v>
       </c>
       <c r="R30" t="n">
-        <v>6827526</v>
+        <v>6827541</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3677,10 +3701,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119587206</v>
+        <v>119585463</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3693,21 +3717,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3717,10 +3741,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480417</v>
+        <v>480192</v>
       </c>
       <c r="R31" t="n">
-        <v>6827436</v>
+        <v>6827498</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3779,10 +3803,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119585182</v>
+        <v>119587607</v>
       </c>
       <c r="B32" t="n">
-        <v>78262</v>
+        <v>77910</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3795,21 +3819,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3819,10 +3843,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480155</v>
+        <v>480173</v>
       </c>
       <c r="R32" t="n">
-        <v>6827454</v>
+        <v>6827470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3881,10 +3905,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119587157</v>
+        <v>119586168</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
+        <v>8432</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3897,21 +3921,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3922,17 +3946,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480388</v>
+        <v>480216</v>
       </c>
       <c r="R33" t="n">
-        <v>6827441</v>
+        <v>6827581</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3959,9 +3983,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3976,19 +4010,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119587429</v>
+        <v>119587342</v>
       </c>
       <c r="B34" t="n">
         <v>91840</v>
@@ -4024,14 +4058,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480241</v>
+        <v>480362</v>
       </c>
       <c r="R34" t="n">
-        <v>6827511</v>
+        <v>6827489</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,10 +4124,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119587456</v>
+        <v>119587254</v>
       </c>
       <c r="B35" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4102,25 +4136,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4130,10 +4164,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480211</v>
+        <v>480368</v>
       </c>
       <c r="R35" t="n">
-        <v>6827485</v>
+        <v>6827434</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4192,10 +4226,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119587161</v>
+        <v>119587683</v>
       </c>
       <c r="B36" t="n">
-        <v>5169</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4208,42 +4242,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100526</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480388</v>
+        <v>480155</v>
       </c>
       <c r="R36" t="n">
-        <v>6827441</v>
+        <v>6827454</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4299,10 +4328,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119586273</v>
+        <v>119586225</v>
       </c>
       <c r="B37" t="n">
-        <v>74638</v>
+        <v>78560</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4315,21 +4344,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4339,10 +4368,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480268</v>
+        <v>480247</v>
       </c>
       <c r="R37" t="n">
-        <v>6827557</v>
+        <v>6827581</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4401,10 +4430,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119585602</v>
+        <v>119586187</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78560</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4417,37 +4446,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480202</v>
+        <v>480220</v>
       </c>
       <c r="R38" t="n">
-        <v>6827537</v>
+        <v>6827593</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4474,19 +4503,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4501,12 +4520,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4615,7 +4634,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119586108</v>
+        <v>119587431</v>
       </c>
       <c r="B40" t="n">
         <v>78526</v>
@@ -4655,10 +4674,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480218</v>
+        <v>480241</v>
       </c>
       <c r="R40" t="n">
-        <v>6827576</v>
+        <v>6827511</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4717,10 +4736,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119585255</v>
+        <v>119586273</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4733,21 +4752,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4757,10 +4776,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480178</v>
+        <v>480268</v>
       </c>
       <c r="R41" t="n">
-        <v>6827488</v>
+        <v>6827557</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4819,10 +4838,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119587438</v>
+        <v>119585182</v>
       </c>
       <c r="B42" t="n">
-        <v>96868</v>
+        <v>78262</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4831,25 +4850,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221941</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4859,10 +4878,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480241</v>
+        <v>480155</v>
       </c>
       <c r="R42" t="n">
-        <v>6827511</v>
+        <v>6827454</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4921,10 +4940,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119585956</v>
+        <v>119586241</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4933,50 +4952,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480186</v>
+        <v>480249</v>
       </c>
       <c r="R43" t="n">
-        <v>6827553</v>
+        <v>6827569</v>
       </c>
       <c r="S43" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5003,19 +5013,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5030,22 +5030,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119587607</v>
+        <v>119587602</v>
       </c>
       <c r="B44" t="n">
-        <v>77910</v>
+        <v>77458</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5058,21 +5058,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611515</v>
+        <v>119611870</v>
       </c>
       <c r="B45" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5160,34 +5160,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480167</v>
+        <v>480264</v>
       </c>
       <c r="R45" t="n">
-        <v>6827463</v>
+        <v>6827609</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5222,40 +5222,34 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>25-tal</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611519</v>
+        <v>119611515</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5268,21 +5262,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5292,10 +5286,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480375</v>
+        <v>480167</v>
       </c>
       <c r="R46" t="n">
-        <v>6827495</v>
+        <v>6827463</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5330,12 +5324,18 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>25-tal</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5354,10 +5354,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119611520</v>
+        <v>119586315</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>5189</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5366,41 +5366,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480256</v>
+        <v>480225</v>
       </c>
       <c r="R47" t="n">
-        <v>6827528</v>
+        <v>6827599</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5427,9 +5427,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5444,12 +5454,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5564,10 +5574,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119611521</v>
+        <v>119611872</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5576,38 +5586,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480342</v>
+        <v>480180</v>
       </c>
       <c r="R49" t="n">
-        <v>6827505</v>
+        <v>6827559</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5642,40 +5652,34 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>6 fk</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119611517</v>
+        <v>119611520</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5688,21 +5692,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5712,10 +5716,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480379</v>
+        <v>480256</v>
       </c>
       <c r="R50" t="n">
-        <v>6827494</v>
+        <v>6827528</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5750,18 +5754,12 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>10 fk</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5780,10 +5778,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119586315</v>
+        <v>119611871</v>
       </c>
       <c r="B51" t="n">
-        <v>5189</v>
+        <v>78526</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5792,41 +5790,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480225</v>
+        <v>480201</v>
       </c>
       <c r="R51" t="n">
-        <v>6827599</v>
+        <v>6827577</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5853,19 +5851,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5892,7 +5880,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119611870</v>
+        <v>119611518</v>
       </c>
       <c r="B52" t="n">
         <v>78526</v>
@@ -5928,14 +5916,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480264</v>
+        <v>480400</v>
       </c>
       <c r="R52" t="n">
-        <v>6827609</v>
+        <v>6827491</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5970,6 +5958,11 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5982,22 +5975,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119611871</v>
+        <v>119611866</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6010,21 +6003,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6034,10 +6027,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480201</v>
+        <v>480364</v>
       </c>
       <c r="R53" t="n">
-        <v>6827577</v>
+        <v>6827460</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6096,7 +6089,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119611518</v>
+        <v>119611519</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6136,10 +6129,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480400</v>
+        <v>480375</v>
       </c>
       <c r="R54" t="n">
-        <v>6827491</v>
+        <v>6827495</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6172,11 +6165,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6203,10 +6191,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119611866</v>
+        <v>119611517</v>
       </c>
       <c r="B55" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6219,34 +6207,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480364</v>
+        <v>480379</v>
       </c>
       <c r="R55" t="n">
-        <v>6827460</v>
+        <v>6827494</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6281,34 +6269,40 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>10 fk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119611872</v>
+        <v>119611521</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6317,38 +6311,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480180</v>
+        <v>480342</v>
       </c>
       <c r="R56" t="n">
-        <v>6827559</v>
+        <v>6827505</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6383,31 +6377,37 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>6 fk</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119672739</v>
+        <v>119672738</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480259</v>
+        <v>480261</v>
       </c>
       <c r="R57" t="n">
-        <v>6827567</v>
+        <v>6827555</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119672740</v>
+        <v>119672749</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480203</v>
+        <v>480345</v>
       </c>
       <c r="R58" t="n">
-        <v>6827555</v>
+        <v>6827530</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119672738</v>
+        <v>119672747</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>5169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6623,25 +6623,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>480261</v>
+        <v>480329</v>
       </c>
       <c r="R59" t="n">
-        <v>6827555</v>
+        <v>6827536</v>
       </c>
       <c r="S59" t="n">
         <v>1</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119672749</v>
+        <v>119672723</v>
       </c>
       <c r="B60" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480345</v>
+        <v>480212</v>
       </c>
       <c r="R60" t="n">
-        <v>6827530</v>
+        <v>6827496</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119672723</v>
+        <v>119672739</v>
       </c>
       <c r="B61" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6831,21 +6831,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480212</v>
+        <v>480259</v>
       </c>
       <c r="R61" t="n">
-        <v>6827496</v>
+        <v>6827567</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119672744</v>
+        <v>119672737</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6929,25 +6929,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480179</v>
+        <v>480227</v>
       </c>
       <c r="R62" t="n">
-        <v>6827552</v>
+        <v>6827511</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119672747</v>
+        <v>119672741</v>
       </c>
       <c r="B63" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7031,25 +7031,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>480329</v>
+        <v>480176</v>
       </c>
       <c r="R63" t="n">
-        <v>6827536</v>
+        <v>6827531</v>
       </c>
       <c r="S63" t="n">
         <v>1</v>
@@ -7325,7 +7325,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119672746</v>
+        <v>119672744</v>
       </c>
       <c r="B66" t="n">
         <v>91840</v>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480170</v>
+        <v>480179</v>
       </c>
       <c r="R66" t="n">
-        <v>6827542</v>
+        <v>6827552</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7427,10 +7427,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119672724</v>
+        <v>119672746</v>
       </c>
       <c r="B67" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7439,25 +7439,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480212</v>
+        <v>480170</v>
       </c>
       <c r="R67" t="n">
-        <v>6827501</v>
+        <v>6827542</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119672737</v>
+        <v>119672724</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7545,21 +7545,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480227</v>
+        <v>480212</v>
       </c>
       <c r="R68" t="n">
-        <v>6827511</v>
+        <v>6827501</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119672741</v>
+        <v>119672740</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480176</v>
+        <v>480203</v>
       </c>
       <c r="R69" t="n">
-        <v>6827531</v>
+        <v>6827555</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119711100</v>
+        <v>119711097</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480230</v>
+        <v>480360</v>
       </c>
       <c r="R72" t="n">
-        <v>6827520</v>
+        <v>6827488</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119711097</v>
+        <v>119711093</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8055,21 +8055,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480360</v>
+        <v>480165</v>
       </c>
       <c r="R73" t="n">
-        <v>6827488</v>
+        <v>6827514</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119711093</v>
+        <v>119711100</v>
       </c>
       <c r="B74" t="n">
-        <v>89633</v>
+        <v>78526</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8157,21 +8157,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480165</v>
+        <v>480230</v>
       </c>
       <c r="R74" t="n">
-        <v>6827514</v>
+        <v>6827520</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119586928</v>
+        <v>119587206</v>
       </c>
       <c r="B2" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480330</v>
+        <v>480417</v>
       </c>
       <c r="R2" t="n">
-        <v>6827548</v>
+        <v>6827436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119585956</v>
+        <v>119586928</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>77458</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480186</v>
+        <v>480330</v>
       </c>
       <c r="R3" t="n">
-        <v>6827553</v>
+        <v>6827548</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,19 +850,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119587206</v>
+        <v>119585956</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,41 +891,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480417</v>
+        <v>480186</v>
       </c>
       <c r="R4" t="n">
-        <v>6827436</v>
+        <v>6827553</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,9 +961,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +988,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119587585</v>
+        <v>119586591</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,50 +1012,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480184</v>
+        <v>480309</v>
       </c>
       <c r="R5" t="n">
-        <v>6827450</v>
+        <v>6827520</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,19 +1073,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,22 +1090,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119586591</v>
+        <v>119587585</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,41 +1114,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480309</v>
+        <v>480184</v>
       </c>
       <c r="R6" t="n">
-        <v>6827520</v>
+        <v>6827450</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,9 +1184,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,12 +1211,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119587456</v>
+        <v>119586694</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>74638</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,34 +3513,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480211</v>
+        <v>480364</v>
       </c>
       <c r="R29" t="n">
-        <v>6827485</v>
+        <v>6827541</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119586694</v>
+        <v>119587456</v>
       </c>
       <c r="B30" t="n">
-        <v>74638</v>
+        <v>91884</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,34 +3615,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480364</v>
+        <v>480211</v>
       </c>
       <c r="R30" t="n">
-        <v>6827541</v>
+        <v>6827485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119587206</v>
+        <v>119587429</v>
       </c>
       <c r="B2" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480417</v>
+        <v>480241</v>
       </c>
       <c r="R2" t="n">
-        <v>6827436</v>
+        <v>6827511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119586928</v>
+        <v>119585602</v>
       </c>
       <c r="B3" t="n">
-        <v>77458</v>
+        <v>78526</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480330</v>
+        <v>480202</v>
       </c>
       <c r="R3" t="n">
-        <v>6827548</v>
+        <v>6827537</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,9 +850,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119585956</v>
+        <v>119586520</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,50 +901,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>480186</v>
+        <v>480299</v>
       </c>
       <c r="R4" t="n">
-        <v>6827553</v>
+        <v>6827540</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,19 +962,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,22 +979,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119586591</v>
+        <v>119587024</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>480309</v>
+        <v>480345</v>
       </c>
       <c r="R5" t="n">
-        <v>6827520</v>
+        <v>6827502</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119587585</v>
+        <v>119586928</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>77458</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,46 +1109,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>480184</v>
+        <v>480330</v>
       </c>
       <c r="R6" t="n">
-        <v>6827450</v>
+        <v>6827548</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,19 +1166,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>18:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1211,22 +1183,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119585640</v>
+        <v>119587161</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>5169</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,37 +1211,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>480227</v>
+        <v>480388</v>
       </c>
       <c r="R7" t="n">
-        <v>6827526</v>
+        <v>6827441</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119586966</v>
+        <v>119585186</v>
       </c>
       <c r="B8" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,34 +1318,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>480330</v>
+        <v>480155</v>
       </c>
       <c r="R8" t="n">
-        <v>6827548</v>
+        <v>6827454</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119586559</v>
+        <v>119587179</v>
       </c>
       <c r="B9" t="n">
         <v>78526</v>
@@ -1463,14 +1440,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>480309</v>
+        <v>480380</v>
       </c>
       <c r="R9" t="n">
-        <v>6827520</v>
+        <v>6827425</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119587179</v>
+        <v>119586168</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>8432</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,41 +1518,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>480380</v>
+        <v>480216</v>
       </c>
       <c r="R10" t="n">
-        <v>6827425</v>
+        <v>6827581</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1602,9 +1584,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,22 +1611,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119586193</v>
+        <v>119587438</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1647,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1671,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>480220</v>
+        <v>480241</v>
       </c>
       <c r="R11" t="n">
-        <v>6827593</v>
+        <v>6827511</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1835,10 +1827,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119585186</v>
+        <v>119587254</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1847,25 +1839,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1875,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>480155</v>
+        <v>480368</v>
       </c>
       <c r="R13" t="n">
-        <v>6827454</v>
+        <v>6827434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1937,10 +1929,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119586076</v>
+        <v>119587607</v>
       </c>
       <c r="B14" t="n">
-        <v>78262</v>
+        <v>77910</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1953,21 +1945,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1977,10 +1969,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>480203</v>
+        <v>480173</v>
       </c>
       <c r="R14" t="n">
-        <v>6827559</v>
+        <v>6827470</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,10 +2031,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119587161</v>
+        <v>119587206</v>
       </c>
       <c r="B15" t="n">
-        <v>5169</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2051,46 +2043,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>480388</v>
+        <v>480417</v>
       </c>
       <c r="R15" t="n">
-        <v>6827441</v>
+        <v>6827436</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119585762</v>
+        <v>119585640</v>
       </c>
       <c r="B16" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2158,25 +2145,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2186,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>480196</v>
+        <v>480227</v>
       </c>
       <c r="R16" t="n">
-        <v>6827538</v>
+        <v>6827526</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119587775</v>
+        <v>119587683</v>
       </c>
       <c r="B17" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2260,41 +2247,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>480151</v>
+        <v>480155</v>
       </c>
       <c r="R17" t="n">
-        <v>6827452</v>
+        <v>6827454</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,19 +2308,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2348,22 +2325,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119586658</v>
+        <v>119586273</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>74638</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2376,34 +2353,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>480377</v>
+        <v>480268</v>
       </c>
       <c r="R18" t="n">
-        <v>6827539</v>
+        <v>6827557</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119587438</v>
+        <v>119586694</v>
       </c>
       <c r="B19" t="n">
-        <v>96868</v>
+        <v>74638</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2474,38 +2451,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>480241</v>
+        <v>480364</v>
       </c>
       <c r="R19" t="n">
-        <v>6827511</v>
+        <v>6827541</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119587157</v>
+        <v>119586658</v>
       </c>
       <c r="B20" t="n">
-        <v>5189</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2576,46 +2553,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>480388</v>
+        <v>480377</v>
       </c>
       <c r="R20" t="n">
-        <v>6827441</v>
+        <v>6827539</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2671,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119587429</v>
+        <v>119586225</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>78560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2683,25 +2655,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2711,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>480241</v>
+        <v>480247</v>
       </c>
       <c r="R21" t="n">
-        <v>6827511</v>
+        <v>6827581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2773,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119586446</v>
+        <v>119586591</v>
       </c>
       <c r="B22" t="n">
-        <v>82305</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2785,38 +2757,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>480268</v>
+        <v>480309</v>
       </c>
       <c r="R22" t="n">
-        <v>6827557</v>
+        <v>6827520</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119586177</v>
+        <v>119587456</v>
       </c>
       <c r="B23" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2891,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2915,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>480220</v>
+        <v>480211</v>
       </c>
       <c r="R23" t="n">
-        <v>6827593</v>
+        <v>6827485</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,10 +2949,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119586108</v>
+        <v>119587157</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>5189</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2989,41 +2961,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>105930</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>480218</v>
+        <v>480388</v>
       </c>
       <c r="R24" t="n">
-        <v>6827576</v>
+        <v>6827441</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3079,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119587094</v>
+        <v>119586177</v>
       </c>
       <c r="B25" t="n">
         <v>78526</v>
@@ -3115,14 +3092,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>480375</v>
+        <v>480220</v>
       </c>
       <c r="R25" t="n">
-        <v>6827471</v>
+        <v>6827593</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,10 +3158,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119585602</v>
+        <v>119585182</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3197,37 +3174,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>480202</v>
+        <v>480155</v>
       </c>
       <c r="R26" t="n">
-        <v>6827537</v>
+        <v>6827454</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3254,19 +3231,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,22 +3248,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119585255</v>
+        <v>119586076</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3309,21 +3276,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3333,10 +3300,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>480178</v>
+        <v>480203</v>
       </c>
       <c r="R27" t="n">
-        <v>6827488</v>
+        <v>6827559</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3395,7 +3362,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119586520</v>
+        <v>119587431</v>
       </c>
       <c r="B28" t="n">
         <v>78526</v>
@@ -3431,14 +3398,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>480299</v>
+        <v>480241</v>
       </c>
       <c r="R28" t="n">
-        <v>6827540</v>
+        <v>6827511</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3497,10 +3464,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119586694</v>
+        <v>119586446</v>
       </c>
       <c r="B29" t="n">
-        <v>74638</v>
+        <v>82305</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3513,34 +3480,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>480364</v>
+        <v>480268</v>
       </c>
       <c r="R29" t="n">
-        <v>6827541</v>
+        <v>6827557</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3599,10 +3566,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119587456</v>
+        <v>119586187</v>
       </c>
       <c r="B30" t="n">
-        <v>91884</v>
+        <v>78560</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3615,21 +3582,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3639,10 +3606,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>480211</v>
+        <v>480220</v>
       </c>
       <c r="R30" t="n">
-        <v>6827485</v>
+        <v>6827593</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3701,10 +3668,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119585463</v>
+        <v>119585956</v>
       </c>
       <c r="B31" t="n">
-        <v>78560</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3713,41 +3680,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>480192</v>
+        <v>480186</v>
       </c>
       <c r="R31" t="n">
-        <v>6827498</v>
+        <v>6827553</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3774,9 +3750,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3791,22 +3777,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119587607</v>
+        <v>119585463</v>
       </c>
       <c r="B32" t="n">
-        <v>77910</v>
+        <v>78560</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3819,21 +3805,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3843,10 +3829,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>480173</v>
+        <v>480192</v>
       </c>
       <c r="R32" t="n">
-        <v>6827470</v>
+        <v>6827498</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3905,10 +3891,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119586168</v>
+        <v>119587775</v>
       </c>
       <c r="B33" t="n">
-        <v>8432</v>
+        <v>78262</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3917,43 +3903,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>480216</v>
+        <v>480151</v>
       </c>
       <c r="R33" t="n">
-        <v>6827581</v>
+        <v>6827452</v>
       </c>
       <c r="S33" t="n">
         <v>9</v>
@@ -3985,7 +3966,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3995,7 +3976,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4022,10 +4003,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119587342</v>
+        <v>119586241</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4034,38 +4015,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rävtjärnen, Dlr</t>
+          <t>Skarpabborrtjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>480362</v>
+        <v>480249</v>
       </c>
       <c r="R34" t="n">
-        <v>6827489</v>
+        <v>6827569</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4124,7 +4105,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119587254</v>
+        <v>119587342</v>
       </c>
       <c r="B35" t="n">
         <v>91840</v>
@@ -4160,14 +4141,14 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>480368</v>
+        <v>480362</v>
       </c>
       <c r="R35" t="n">
-        <v>6827434</v>
+        <v>6827489</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4226,10 +4207,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119587683</v>
+        <v>119586966</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4238,38 +4219,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>480155</v>
+        <v>480330</v>
       </c>
       <c r="R36" t="n">
-        <v>6827454</v>
+        <v>6827548</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4328,10 +4309,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119586225</v>
+        <v>119587094</v>
       </c>
       <c r="B37" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4344,34 +4325,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>480247</v>
+        <v>480375</v>
       </c>
       <c r="R37" t="n">
-        <v>6827581</v>
+        <v>6827471</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4430,10 +4411,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119586187</v>
+        <v>119586108</v>
       </c>
       <c r="B38" t="n">
-        <v>78560</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4446,21 +4427,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4470,10 +4451,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>480220</v>
+        <v>480218</v>
       </c>
       <c r="R38" t="n">
-        <v>6827593</v>
+        <v>6827576</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4532,10 +4513,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119587024</v>
+        <v>119586559</v>
       </c>
       <c r="B39" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4548,21 +4529,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4572,10 +4553,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>480345</v>
+        <v>480309</v>
       </c>
       <c r="R39" t="n">
-        <v>6827502</v>
+        <v>6827520</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4634,10 +4615,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119587431</v>
+        <v>119587602</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>77458</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4650,21 +4631,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4674,10 +4655,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>480241</v>
+        <v>480173</v>
       </c>
       <c r="R40" t="n">
-        <v>6827511</v>
+        <v>6827470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4736,10 +4717,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119586273</v>
+        <v>119585255</v>
       </c>
       <c r="B41" t="n">
-        <v>74638</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4752,21 +4733,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4776,10 +4757,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>480268</v>
+        <v>480178</v>
       </c>
       <c r="R41" t="n">
-        <v>6827557</v>
+        <v>6827488</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4838,10 +4819,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119585182</v>
+        <v>119587585</v>
       </c>
       <c r="B42" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4854,37 +4835,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skarpabborrtjärnarna, Dlr</t>
+          <t>Rävtjärnen, Rävtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>480155</v>
+        <v>480184</v>
       </c>
       <c r="R42" t="n">
-        <v>6827454</v>
+        <v>6827450</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4911,9 +4901,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4928,19 +4928,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119586241</v>
+        <v>119585762</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>480249</v>
+        <v>480196</v>
       </c>
       <c r="R43" t="n">
-        <v>6827569</v>
+        <v>6827538</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5042,10 +5042,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119587602</v>
+        <v>119586193</v>
       </c>
       <c r="B44" t="n">
-        <v>77458</v>
+        <v>91840</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5054,25 +5054,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>480173</v>
+        <v>480220</v>
       </c>
       <c r="R44" t="n">
-        <v>6827470</v>
+        <v>6827593</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5144,10 +5144,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119611870</v>
+        <v>119611515</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5160,34 +5160,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>480264</v>
+        <v>480167</v>
       </c>
       <c r="R45" t="n">
-        <v>6827609</v>
+        <v>6827463</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5222,34 +5222,40 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>25-tal</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119611515</v>
+        <v>119611870</v>
       </c>
       <c r="B46" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5262,34 +5268,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>480167</v>
+        <v>480264</v>
       </c>
       <c r="R46" t="n">
-        <v>6827463</v>
+        <v>6827609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5324,40 +5330,34 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>25-tal</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119586315</v>
+        <v>119611520</v>
       </c>
       <c r="B47" t="n">
-        <v>5189</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5366,41 +5366,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>480225</v>
+        <v>480256</v>
       </c>
       <c r="R47" t="n">
-        <v>6827599</v>
+        <v>6827528</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5427,19 +5427,9 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:34</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-06</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:34</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5454,22 +5444,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119611516</v>
+        <v>119611872</v>
       </c>
       <c r="B48" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5482,34 +5472,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>480383</v>
+        <v>480180</v>
       </c>
       <c r="R48" t="n">
-        <v>6827478</v>
+        <v>6827559</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5544,40 +5534,34 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En fk</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119611872</v>
+        <v>119611521</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5586,38 +5570,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>480180</v>
+        <v>480342</v>
       </c>
       <c r="R49" t="n">
-        <v>6827559</v>
+        <v>6827505</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5652,31 +5636,37 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>6 fk</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119611520</v>
+        <v>119611871</v>
       </c>
       <c r="B50" t="n">
         <v>78526</v>
@@ -5712,14 +5702,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>480256</v>
+        <v>480201</v>
       </c>
       <c r="R50" t="n">
-        <v>6827528</v>
+        <v>6827577</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5766,19 +5756,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119611871</v>
+        <v>119611519</v>
       </c>
       <c r="B51" t="n">
         <v>78526</v>
@@ -5814,14 +5804,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Rävtjärn norra, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>480201</v>
+        <v>480375</v>
       </c>
       <c r="R51" t="n">
-        <v>6827577</v>
+        <v>6827495</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5868,22 +5858,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119611518</v>
+        <v>119611516</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5896,21 +5886,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5920,10 +5910,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>480400</v>
+        <v>480383</v>
       </c>
       <c r="R52" t="n">
-        <v>6827491</v>
+        <v>6827478</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5960,7 +5950,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>En fk</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5969,6 +5959,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5987,10 +5978,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119611866</v>
+        <v>119586315</v>
       </c>
       <c r="B53" t="n">
-        <v>91463</v>
+        <v>5189</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5999,41 +5990,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4745</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Rävtjärn, Dlr</t>
+          <t>Härjamäksbäcken, Härjamäksbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>480364</v>
+        <v>480225</v>
       </c>
       <c r="R53" t="n">
-        <v>6827460</v>
+        <v>6827599</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6060,9 +6051,19 @@
           <t>2024-09-06</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6089,7 +6090,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119611519</v>
+        <v>119611518</v>
       </c>
       <c r="B54" t="n">
         <v>78526</v>
@@ -6129,10 +6130,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>480375</v>
+        <v>480400</v>
       </c>
       <c r="R54" t="n">
-        <v>6827495</v>
+        <v>6827491</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6165,6 +6166,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6191,10 +6197,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119611517</v>
+        <v>119611866</v>
       </c>
       <c r="B55" t="n">
-        <v>91884</v>
+        <v>91463</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6207,34 +6213,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Rävtjärn norra, Dlr</t>
+          <t>Rävtjärn, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>480379</v>
+        <v>480364</v>
       </c>
       <c r="R55" t="n">
-        <v>6827494</v>
+        <v>6827460</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6269,40 +6275,34 @@
           <t>2024-09-06</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>10 fk</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119611521</v>
+        <v>119611517</v>
       </c>
       <c r="B56" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6311,25 +6311,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>480342</v>
+        <v>480379</v>
       </c>
       <c r="R56" t="n">
-        <v>6827505</v>
+        <v>6827494</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6379,7 +6379,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>6 fk</t>
+          <t>10 fk</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6407,7 +6407,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119672738</v>
+        <v>119672739</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6447,10 +6447,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>480261</v>
+        <v>480259</v>
       </c>
       <c r="R57" t="n">
-        <v>6827555</v>
+        <v>6827567</v>
       </c>
       <c r="S57" t="n">
         <v>1</v>
@@ -6509,10 +6509,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119672749</v>
+        <v>119672740</v>
       </c>
       <c r="B58" t="n">
-        <v>91834</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6525,21 +6525,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6549,10 +6549,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>480345</v>
+        <v>480203</v>
       </c>
       <c r="R58" t="n">
-        <v>6827530</v>
+        <v>6827555</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6713,10 +6713,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119672723</v>
+        <v>119672743</v>
       </c>
       <c r="B60" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6725,25 +6725,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>480212</v>
+        <v>480317</v>
       </c>
       <c r="R60" t="n">
-        <v>6827496</v>
+        <v>6827518</v>
       </c>
       <c r="S60" t="n">
         <v>1</v>
@@ -6815,10 +6815,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119672739</v>
+        <v>119672744</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6827,25 +6827,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6855,10 +6855,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>480259</v>
+        <v>480179</v>
       </c>
       <c r="R61" t="n">
-        <v>6827567</v>
+        <v>6827552</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
@@ -6917,10 +6917,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119672737</v>
+        <v>119672749</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6933,21 +6933,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6957,10 +6957,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>480227</v>
+        <v>480345</v>
       </c>
       <c r="R62" t="n">
-        <v>6827511</v>
+        <v>6827530</v>
       </c>
       <c r="S62" t="n">
         <v>1</v>
@@ -7121,7 +7121,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119672743</v>
+        <v>119672742</v>
       </c>
       <c r="B64" t="n">
         <v>91840</v>
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>480317</v>
+        <v>480349</v>
       </c>
       <c r="R64" t="n">
-        <v>6827518</v>
+        <v>6827514</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
@@ -7223,10 +7223,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119672742</v>
+        <v>119672723</v>
       </c>
       <c r="B65" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7235,25 +7235,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7263,10 +7263,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>480349</v>
+        <v>480212</v>
       </c>
       <c r="R65" t="n">
-        <v>6827514</v>
+        <v>6827496</v>
       </c>
       <c r="S65" t="n">
         <v>1</v>
@@ -7325,10 +7325,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119672744</v>
+        <v>119672724</v>
       </c>
       <c r="B66" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7337,25 +7337,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7365,10 +7365,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>480179</v>
+        <v>480212</v>
       </c>
       <c r="R66" t="n">
-        <v>6827552</v>
+        <v>6827501</v>
       </c>
       <c r="S66" t="n">
         <v>1</v>
@@ -7427,10 +7427,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119672746</v>
+        <v>119672737</v>
       </c>
       <c r="B67" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7439,25 +7439,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7467,10 +7467,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>480170</v>
+        <v>480227</v>
       </c>
       <c r="R67" t="n">
-        <v>6827542</v>
+        <v>6827511</v>
       </c>
       <c r="S67" t="n">
         <v>1</v>
@@ -7529,10 +7529,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119672724</v>
+        <v>119672746</v>
       </c>
       <c r="B68" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7541,25 +7541,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480212</v>
+        <v>480170</v>
       </c>
       <c r="R68" t="n">
-        <v>6827501</v>
+        <v>6827542</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119672740</v>
+        <v>119672738</v>
       </c>
       <c r="B69" t="n">
         <v>78526</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480203</v>
+        <v>480261</v>
       </c>
       <c r="R69" t="n">
         <v>6827555</v>
@@ -7733,10 +7733,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119711095</v>
+        <v>119711097</v>
       </c>
       <c r="B70" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7749,21 +7749,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7773,10 +7773,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>480290</v>
+        <v>480360</v>
       </c>
       <c r="R70" t="n">
-        <v>6827524</v>
+        <v>6827488</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119711097</v>
+        <v>119711100</v>
       </c>
       <c r="B72" t="n">
         <v>78526</v>
@@ -7977,10 +7977,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>480360</v>
+        <v>480230</v>
       </c>
       <c r="R72" t="n">
-        <v>6827488</v>
+        <v>6827520</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119711093</v>
+        <v>119711095</v>
       </c>
       <c r="B73" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8055,21 +8055,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>480165</v>
+        <v>480290</v>
       </c>
       <c r="R73" t="n">
-        <v>6827514</v>
+        <v>6827524</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8141,10 +8141,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119711100</v>
+        <v>119711096</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8157,21 +8157,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>480230</v>
+        <v>480307</v>
       </c>
       <c r="R74" t="n">
-        <v>6827520</v>
+        <v>6827579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8243,10 +8243,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119711096</v>
+        <v>119711093</v>
       </c>
       <c r="B75" t="n">
-        <v>78262</v>
+        <v>89633</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8259,21 +8259,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>480307</v>
+        <v>480165</v>
       </c>
       <c r="R75" t="n">
-        <v>6827579</v>
+        <v>6827514</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -7529,10 +7529,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119672746</v>
+        <v>119672738</v>
       </c>
       <c r="B68" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7541,25 +7541,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480170</v>
+        <v>480261</v>
       </c>
       <c r="R68" t="n">
-        <v>6827542</v>
+        <v>6827555</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119672738</v>
+        <v>119672746</v>
       </c>
       <c r="B69" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7643,25 +7643,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480261</v>
+        <v>480170</v>
       </c>
       <c r="R69" t="n">
-        <v>6827555</v>
+        <v>6827542</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>

--- a/artfynd/A 38960-2022 artfynd.xlsx
+++ b/artfynd/A 38960-2022 artfynd.xlsx
@@ -7529,10 +7529,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119672738</v>
+        <v>119672746</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7541,25 +7541,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>480261</v>
+        <v>480170</v>
       </c>
       <c r="R68" t="n">
-        <v>6827555</v>
+        <v>6827542</v>
       </c>
       <c r="S68" t="n">
         <v>1</v>
@@ -7631,10 +7631,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119672746</v>
+        <v>119672738</v>
       </c>
       <c r="B69" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7643,25 +7643,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7671,10 +7671,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>480170</v>
+        <v>480261</v>
       </c>
       <c r="R69" t="n">
-        <v>6827542</v>
+        <v>6827555</v>
       </c>
       <c r="S69" t="n">
         <v>1</v>
